--- a/src/test/resources/api_data/datasets/dataset_errorValidation.xlsx
+++ b/src/test/resources/api_data/datasets/dataset_errorValidation.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gmena\Java_DEMO\Herokuapp\src\test\resources\api_data\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A57DDEF-B5D4-40ED-B798-2475DB3467CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436A68B0-733E-4BE6-A13F-36DB92915B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="27">
   <si>
     <t>firstName</t>
   </si>
@@ -106,235 +106,12 @@
   </si>
   <si>
     <t>123456789</t>
-  </si>
-  <si>
-    <t>69cce09b23b8a000159cb131</t>
-  </si>
-  <si>
-    <t>69cce09ce174bc00158a2765</t>
-  </si>
-  <si>
-    <t>69cce11023b8a000159cb133</t>
-  </si>
-  <si>
-    <t>69cce112e174bc00158a276a</t>
-  </si>
-  <si>
-    <t>69cce1b4e174bc00158a276c</t>
-  </si>
-  <si>
-    <t>69cce1b623b8a000159cb135</t>
-  </si>
-  <si>
-    <t>69cce1b8e174bc00158a276e</t>
-  </si>
-  <si>
-    <t>69cce1bb23b8a000159cb137</t>
-  </si>
-  <si>
-    <t>69cce1bd23b8a000159cb139</t>
-  </si>
-  <si>
-    <t>69cce1bfe174bc00158a276f</t>
-  </si>
-  <si>
-    <t>69cce1c123b8a000159cb13c</t>
-  </si>
-  <si>
-    <t>69cce1c323b8a000159cb13d</t>
-  </si>
-  <si>
-    <t>69cce1c5e174bc00158a2772</t>
-  </si>
-  <si>
-    <t>69cce1c7e174bc00158a2773</t>
-  </si>
-  <si>
-    <t>69ccf3f3e174bc00158a27d0</t>
-  </si>
-  <si>
-    <t>69ccf3f5e174bc00158a27d2</t>
-  </si>
-  <si>
-    <t>69ccf3f6e174bc00158a27d3</t>
-  </si>
-  <si>
-    <t>69ccf3f823b8a000159cb193</t>
-  </si>
-  <si>
-    <t>69ccf3f9e174bc00158a27d6</t>
-  </si>
-  <si>
-    <t>69ccf3fb23b8a000159cb194</t>
-  </si>
-  <si>
-    <t>69ccf3fc23b8a000159cb195</t>
-  </si>
-  <si>
-    <t>69ccf3fe23b8a000159cb196</t>
-  </si>
-  <si>
-    <t>69ccf3ffe174bc00158a27da</t>
-  </si>
-  <si>
-    <t>69ccf401e174bc00158a27db</t>
-  </si>
-  <si>
-    <t>69ccf40ae174bc00158a27e5</t>
-  </si>
-  <si>
-    <t>69ccf40ce174bc00158a27e7</t>
-  </si>
-  <si>
-    <t>69ccf40e23b8a000159cb1a2</t>
-  </si>
-  <si>
-    <t>69ccf410e174bc00158a27e8</t>
-  </si>
-  <si>
-    <t>69ccf412e174bc00158a27ea</t>
-  </si>
-  <si>
-    <t>69ccf414e174bc00158a27eb</t>
-  </si>
-  <si>
-    <t>69ccf416e174bc00158a27ed</t>
-  </si>
-  <si>
-    <t>69ccf41823b8a000159cb1a6</t>
-  </si>
-  <si>
-    <t>69ccf41b23b8a000159cb1a7</t>
-  </si>
-  <si>
-    <t>69ccf41de174bc00158a27f0</t>
-  </si>
-  <si>
-    <t>69ccfe73e174bc00158a2866</t>
-  </si>
-  <si>
-    <t>69ccfe74e174bc00158a2868</t>
-  </si>
-  <si>
-    <t>69ccfe76e174bc00158a286a</t>
-  </si>
-  <si>
-    <t>69ccfe77e174bc00158a286c</t>
-  </si>
-  <si>
-    <t>69ccfe79e174bc00158a286e</t>
-  </si>
-  <si>
-    <t>69ccfe7be174bc00158a2870</t>
-  </si>
-  <si>
-    <t>69ccfe7ce174bc00158a2871</t>
-  </si>
-  <si>
-    <t>69ccfe7ee174bc00158a2872</t>
-  </si>
-  <si>
-    <t>69ccfe7fe174bc00158a2873</t>
-  </si>
-  <si>
-    <t>69ccfe81e174bc00158a2874</t>
-  </si>
-  <si>
-    <t>69ccfe8be174bc00158a287d</t>
-  </si>
-  <si>
-    <t>69ccfe8de174bc00158a287e</t>
-  </si>
-  <si>
-    <t>69ccfe8f23b8a000159cb229</t>
-  </si>
-  <si>
-    <t>69ccfe9123b8a000159cb22a</t>
-  </si>
-  <si>
-    <t>69ccfe9323b8a000159cb22b</t>
-  </si>
-  <si>
-    <t>69ccfe9523b8a000159cb22d</t>
-  </si>
-  <si>
-    <t>69ccfe97e174bc00158a2883</t>
-  </si>
-  <si>
-    <t>69ccfe99e174bc00158a2884</t>
-  </si>
-  <si>
-    <t>69ccfe9b23b8a000159cb230</t>
-  </si>
-  <si>
-    <t>69ccfe9de174bc00158a2886</t>
-  </si>
-  <si>
-    <t>69ccff72e174bc00158a28b9</t>
-  </si>
-  <si>
-    <t>69ccff74e174bc00158a28ba</t>
-  </si>
-  <si>
-    <t>69ccff7523b8a000159cb25a</t>
-  </si>
-  <si>
-    <t>69ccff7723b8a000159cb25c</t>
-  </si>
-  <si>
-    <t>69ccff7823b8a000159cb25d</t>
-  </si>
-  <si>
-    <t>69ccff7ae174bc00158a28be</t>
-  </si>
-  <si>
-    <t>69ccff7be174bc00158a28c0</t>
-  </si>
-  <si>
-    <t>69ccff7de174bc00158a28c1</t>
-  </si>
-  <si>
-    <t>69ccff7ee174bc00158a28c3</t>
-  </si>
-  <si>
-    <t>69ccff80e174bc00158a28c5</t>
-  </si>
-  <si>
-    <t>69ccff8a23b8a000159cb266</t>
-  </si>
-  <si>
-    <t>69ccff8ce174bc00158a28d1</t>
-  </si>
-  <si>
-    <t>69ccff8e23b8a000159cb268</t>
-  </si>
-  <si>
-    <t>69ccff90e174bc00158a28d2</t>
-  </si>
-  <si>
-    <t>69ccff9223b8a000159cb26b</t>
-  </si>
-  <si>
-    <t>69ccff9423b8a000159cb26c</t>
-  </si>
-  <si>
-    <t>69ccff96e174bc00158a28d5</t>
-  </si>
-  <si>
-    <t>69ccff98e174bc00158a28d7</t>
-  </si>
-  <si>
-    <t>69ccff9a23b8a000159cb26e</t>
-  </si>
-  <si>
-    <t>69ccff9c23b8a000159cb270</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -673,7 +450,7 @@
   <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="13" customWidth="true" width="24.140625"/>
+    <col min="2" max="13" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -715,10 +492,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -730,30 +504,27 @@
       <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s" s="0">
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
         <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K2" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L2" t="s" s="0">
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -765,33 +536,30 @@
       <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s" s="0">
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
         <v>10</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K3" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L3" t="s" s="0">
+      <c r="K3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s" s="0">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="1"/>
@@ -801,33 +569,30 @@
       <c r="F4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I4" t="s" s="0">
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
         <v>10</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K4" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L4" t="s" s="0">
+      <c r="K4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s" s="0">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -837,33 +602,30 @@
       <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I5" t="s" s="0">
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
         <v>10</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K5" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L5" t="s" s="0">
+      <c r="K5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s" s="0">
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -873,33 +635,30 @@
         <v>14</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I6" t="s" s="0">
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
         <v>10</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K6" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L6" t="s" s="0">
+      <c r="K6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s" s="0">
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -911,30 +670,27 @@
       <c r="F7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H7" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I7" t="s" s="0">
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
         <v>10</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K7" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L7" t="s" s="0">
+      <c r="K7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s" s="0">
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -946,30 +702,27 @@
       <c r="F8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G8" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I8" t="s" s="0">
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
         <v>10</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K8" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L8" t="s" s="0">
+      <c r="K8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s" s="0">
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -981,30 +734,27 @@
       <c r="F9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G9" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H9" t="s" s="0">
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
         <v>10</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K9" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L9" t="s" s="0">
+      <c r="K9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s" s="0">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1016,31 +766,28 @@
       <c r="F10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G10" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H10" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I10" t="s" s="0">
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" t="s">
         <v>10</v>
       </c>
       <c r="J10" s="1"/>
-      <c r="K10" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L10" t="s" s="0">
+      <c r="K10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s" s="0">
-        <v>88</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s" s="0">
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1052,30 +799,27 @@
       <c r="F11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G11" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H11" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I11" t="s" s="0">
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" t="s">
         <v>10</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L11" t="s" s="0">
+      <c r="L11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s" s="0">
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1087,30 +831,27 @@
       <c r="F12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G12" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H12" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I12" t="s" s="0">
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" t="s">
         <v>10</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K12" t="s" s="0">
+      <c r="K12" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C13" t="s" s="0">
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="1"/>
@@ -1119,13 +860,10 @@
       <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C14" t="s" s="0">
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1137,33 +875,30 @@
       <c r="F14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G14" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H14" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I14" t="s" s="0">
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" t="s">
         <v>10</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K14" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L14" t="s" s="0">
+      <c r="K14" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C15" t="s" s="0">
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1175,33 +910,30 @@
       <c r="F15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G15" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H15" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I15" t="s" s="0">
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" t="s">
         <v>10</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K15" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L15" t="s" s="0">
+      <c r="K15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C16" t="s" s="0">
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -1213,33 +945,30 @@
       <c r="F16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G16" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H16" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I16" t="s" s="0">
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" t="s">
         <v>10</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K16" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L16" t="s" s="0">
+      <c r="K16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s" s="0">
-        <v>96</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C17" t="s" s="0">
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -1251,33 +980,30 @@
       <c r="F17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G17" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H17" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I17" t="s" s="0">
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" t="s">
         <v>10</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K17" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L17" t="s" s="0">
+      <c r="K17" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s" s="0">
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -1289,33 +1015,30 @@
       <c r="F18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G18" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H18" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I18" t="s" s="0">
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" t="s">
         <v>10</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K18" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L18" t="s" s="0">
+      <c r="K18" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s" s="0">
-        <v>98</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C19" t="s" s="0">
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -1327,33 +1050,30 @@
       <c r="F19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G19" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H19" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I19" t="s" s="0">
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" t="s">
         <v>10</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K19" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L19" t="s" s="0">
+      <c r="K19" t="s">
+        <v>11</v>
+      </c>
+      <c r="L19" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C20" t="s" s="0">
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -1365,30 +1085,27 @@
       <c r="F20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G20" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H20" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I20" t="s" s="0">
+      <c r="G20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" t="s">
         <v>10</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K20" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L20" t="s" s="0">
+      <c r="K20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="C21" t="s" s="0">
+      <c r="C21" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -1400,22 +1117,22 @@
       <c r="F21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G21" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H21" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="I21" t="s" s="0">
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" t="s">
         <v>10</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K21" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="L21" t="s" s="0">
+      <c r="K21" t="s">
+        <v>11</v>
+      </c>
+      <c r="L21" t="s">
         <v>12</v>
       </c>
     </row>
